--- a/tame_output/ON/bt/strategyON_20240114.xlsx
+++ b/tame_output/ON/bt/strategyON_20240114.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.2%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-12</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1841"/>
+  <dimension ref="A1:G1842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.298466227775266</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43904,6 +43904,29 @@
       </c>
       <c r="G1841" t="n">
         <v>4.479954919408142</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="2" t="n">
+        <v>45304</v>
+      </c>
+      <c r="B1842" t="n">
+        <v>3.293724427206153</v>
+      </c>
+      <c r="C1842" t="n">
+        <v>3.13585268755003</v>
+      </c>
+      <c r="D1842" t="n">
+        <v>1.64173331998302</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>3.79218959122949</v>
+      </c>
+      <c r="F1842" t="n">
+        <v>2.241866401647637</v>
+      </c>
+      <c r="G1842" t="n">
+        <v>4.480972528538612</v>
       </c>
     </row>
   </sheetData>
